--- a/AmiAmi_sales.xlsx
+++ b/AmiAmi_sales.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="393">
   <si>
     <t>Condition</t>
   </si>
@@ -40,6 +40,9 @@
     <t>Discount %</t>
   </si>
   <si>
+    <t>Pre-owned</t>
+  </si>
+  <si>
     <t>Sale</t>
   </si>
   <si>
@@ -49,19 +52,169 @@
     <t>New</t>
   </si>
   <si>
+    <t>THE IDOLM@STER Cinderella Girls Nagi Hisakawa 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Girls' Frontline MDR Cocktail Observer Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
     <t>Super Sonico 10th Merry Christmas! 1/7 Complete Figure</t>
   </si>
   <si>
-    <t>[Exclusive Sale] V ayamy Cat Ver. 1/7 Complete Figure</t>
+    <t>Azur Lane Bremerton Kung Fu Cruiser Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Hyakka Ryoran: Samurai Girls - Senhime Swimsuit ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>[Bonus] XIAMI Fortunate to Meet Chinese Dress Ver. Set 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Meido-Busou: Javelin 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Battle! Costume Maid Watch Maid 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>"Phantasy Star Online 2 es" Gene [Summer Vacation] 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>THE IDOLM@STER Cinderella Girls - Ranko Kanzaki Bara no Yami-hime Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Girls und Panzer Senshadou Daisakusen! Shiho Nishizumi [Oarai Girls High] 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Girls' Frontline DP-12 Morning Fable Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>[Bonus] Niya Hidden Forest Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Tatsu Chan 1/7 Scale Figure</t>
+  </si>
+  <si>
+    <t>KDcolle Saekano: How to Raise a Boring Girlfriend Megumi Kato Pillow Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>King's Proposal Saika Kuozaki 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>[AmiAmi Exclusive Bonus] [AmiAmi Limited Edition] Azur Lane "Kersaint: Reverent Runner" 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>[Bonus] Rabbit Flova 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Sonic Soldier Borgman Anice Farm [Memories style] 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>[Bonus] Azur Lane Kearsarge All-Night Charge Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Umamusume Pretty Derby Eishin Flash 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Goddess of Victory: Nikke Anis: Sparkling Summer 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Overlord Albedo 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Re:ZERO -Starting Life in Another World- Rem AxA -SF SpaceSuit- 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>"Date A Live IV" Tohka Yatogami -Princess Amethyst Dress Ver.- 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>"Chainsaw Man" Chainsaw Man 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>BOFURI: I Don't Want to Get Hurt, so I'll Max Out My Defense. 2 Maple Original Armor ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>ATRI -My Dear Moments- Atri Pajama Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Love Live! Sunshine!! Riko Sakurauchi Special 7ver. 1/7 Complete Figure [7net Shopping Exclusive]</t>
+  </si>
+  <si>
+    <t>Blue Archive Karin Kakudate (Bunny Girl) Game Playing Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Blue Archive Asuna Ichinose (Bunny Girl) Game Playing Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>[Bonus] Azur Lane Ulrich von Hutten Ignition Matrician Ver. 1/7 Complete Figure</t>
   </si>
   <si>
     <t>Genshin Impact Eula: Wavecrest Waltz Ver. 1/7 Complete Figure</t>
   </si>
   <si>
-    <t>Goddess of Victory: Nikke Anis: Sparkling Summer 1/7 Complete Figure</t>
-  </si>
-  <si>
-    <t>[AmiAmi Exclusive Bonus] [Exclusive Sale] Azur Lane Glorious Chinese New Year Ver. 1/7 Complete Figure</t>
+    <t>The Quintessential Quintuplets SS Yotsuba Nakano Fallen Angel ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>TV Anime "Azur Lane Slow Ahead!" Honolulu Yukata Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>[Bonus] Honkai: Star Rail Dan Heng/Imbibitor Lunae DX Edition 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Atelier Yumia: The Alchemist of Memories &amp; the Envisioned Land Yumia Liessfeldt DX Edition 1/7 Complete Figure (Gust Shop Exclusive)</t>
+  </si>
+  <si>
+    <t>[Bonus] Nekopara Chocola &amp; Vanilla Dream of Eden ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Goddess of Victory: Nikke Noir: Black Rabbit 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>PRISMA WING The Case Study of Vanitas Vanitas 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Goddess of Victory: Nikke Blanc: White Rabbit 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Monogatari Series Hitagi Senjyogahara: Letter to You 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>hololive Hoshimachi Suisei 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Azur Lane Perseus Light Armor Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Hell's Paradise: Jigokuraku Gabimaru 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>KDcolle The Angel Next Door Spoils Me Rotten Mahiru Shiina Tea Party ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>"GUILTY GEAR -STRIVE-" Bridget 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Umamusume Pretty Derby Twin Turbo 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>TV Anime "Lycoris Recoil" Takina Inoue 1/7 Complete Figure (Aniplex Online Exclusive)</t>
+  </si>
+  <si>
+    <t>Absent-minded JK Hina Aiuchi Another Color 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Majo no Tabitabi Elaina -Early Summer Sky- 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>KDcolle "Fate/Grand Order" Foreigner/Mysterious Heroine XX 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>[AmiAmi Exclusive Bonus] Azur Lane August von Parseval The Conquered Unhulde Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Fire Emblem Edelgard 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Summer Pockets REFLECTION BLUE Shiroha Naruse 1/7 Complete Figure</t>
   </si>
   <si>
     <t>Character Vocal Series 01 Hatsune Miku feat. Yoneyama Mai 1/7 Complete Figure</t>
@@ -70,7 +223,25 @@
     <t>Blue Archive Kakudate Karin (Bunny Girl) 1/7 Complete Figure</t>
   </si>
   <si>
-    <t>Fate/Grand Order Berserker/Sei Shounagon 1/7 Complete Figure</t>
+    <t>[Bonus] Arknights Texas the Omertosa Yi Jun VER. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>[Bonus] Steins;Gate Mayuri Shiina Swimsuit Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>[Exclusive Sale] White Rabbit Rosu Underwear Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>SNK Bishoujo Leona Heidern -THE KING OF FIGHTERS '97- 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Lycoris Recoil Chisato Nishikigi: Oversized Sweatshirt Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>[Bonus] Azur Lane Bremerton Still Illustration Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>The 7 Deadly Sins Maou Mokushiroku Shitto no Shou - Leviathan Hanketsu Hot Pants no Setsu Momoiro no Itadaki 1/7 Complete Figure</t>
   </si>
   <si>
     <t>Blue Archive Toki (Bunny Girl) Memorial Lobby Ver. 1/7 Complete Figure</t>
@@ -82,25 +253,184 @@
     <t>MONSTER HIGH BISHOUJO Draculaura 1/7 Complete Figure</t>
   </si>
   <si>
-    <t>Azur Lane Shimakaze: Clumsy Moon Rabbit 1/7 Complete Figure</t>
+    <t>BOCCHI THE ROCK! Hitori Gotoh 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Houkai Gakuen Seele Vollerei Shippo Yuri Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>[Bonus] Azur Lane Prinz Eugen (Hyakka Ryoran ver.) 1/7 Complete Figure [Kotobukiya Shop Exclusive]</t>
   </si>
   <si>
     <t>[Bonus] Honkai: Star Rail Kafka 1/7 Complete Figure</t>
   </si>
   <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-119521-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-134416-R</t>
+  </si>
+  <si>
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-149078</t>
   </si>
   <si>
-    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-172144</t>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-153747-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIG-MOE-2568-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-165964</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-142564-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-141897-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-156367-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-029344-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-159851-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-175334-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-179308</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-181608</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-052424-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-173949-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-182418-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-177849</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-162960-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-176220</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-175857-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-177147-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-176776-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-162548</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-174051</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-142203</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-151126</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-185558</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-040862-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-164274-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-150878-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-180136-R</t>
   </si>
   <si>
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-181372</t>
   </si>
   <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-149160</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-195630-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-171348</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-194880-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-170430</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-182256</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-170231</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-183285</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-178266</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-167690</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-166148</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-154014</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-189470</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-160173-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-176926-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-171169-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-174007-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-152018-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-119561-R</t>
+  </si>
+  <si>
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-177147</t>
   </si>
   <si>
-    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-180313</t>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-177576-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-180343</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-182741</t>
   </si>
   <si>
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-171858</t>
@@ -109,7 +439,25 @@
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-185231</t>
   </si>
   <si>
-    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-185101</t>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-187543</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-184860</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-191901</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-173862</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-186836-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-184035</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-019476-R</t>
   </si>
   <si>
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-185454</t>
@@ -121,25 +469,187 @@
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-189605</t>
   </si>
   <si>
-    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-185281</t>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-159024-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-133587-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-180136</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-049232-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-171858-R</t>
   </si>
   <si>
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-181818</t>
   </si>
   <si>
+    <t>https://img.amiami.com/images/product/main/204/FIGURE-119521.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/214/FIGURE-134416.jpg</t>
+  </si>
+  <si>
     <t>https://img.amiami.com/images/product/main/224/FIGURE-149078.jpg</t>
   </si>
   <si>
-    <t>https://img.amiami.com/images/product/main/242/FIGURE-172144.jpg</t>
+    <t>https://img.amiami.com/images/product/main/232/FIGURE-153747.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/112/FIG-MOE-2568.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/241/FIGURE-165964.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/223/FIGURE-142564.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/222/FIGURE-141897.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/232/FIGURE-156367.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/172/FIGURE-029344.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/233/FIGURE-159851.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/243/FIGURE-175334.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/244/FIGURE-179308.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/251/FIGURE-181608.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/193/FIGURE-052424.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/243/FIGURE-173949.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/251/FIGURE-182418.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/244/FIGURE-177849.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/234/FIGURE-162960.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/243/FIGURE-176220.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/243/FIGURE-175857.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/244/FIGURE-177147.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/244/FIGURE-176776.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/234/FIGURE-162548.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/243/FIGURE-174051.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/223/FIGURE-142203.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/231/FIGURE-151126.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/252/FIGURE-185558.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/183/FIGURE-040862.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/234/FIGURE-164274.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/231/FIGURE-150878.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/244/FIGURE-180136.jpg</t>
   </si>
   <si>
     <t>https://img.amiami.com/images/product/main/251/FIGURE-181372.jpg</t>
   </si>
   <si>
-    <t>https://img.amiami.com/images/product/main/244/FIGURE-177147.jpg</t>
-  </si>
-  <si>
-    <t>https://img.amiami.com/images/product/main/244/FIGURE-180313.jpg</t>
+    <t>https://img.amiami.com/images/product/main/224/FIGURE-149160.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/254/FIGURE-195630.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/242/FIGURE-171348.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/254/FIGURE-194880.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/242/FIGURE-170430.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/251/FIGURE-182256.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/242/FIGURE-170231.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/251/FIGURE-183285.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/244/FIGURE-178266.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/241/FIGURE-167690.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/241/FIGURE-166148.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/232/FIGURE-154014.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/253/FIGURE-189470.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/233/FIGURE-160173.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/244/FIGURE-176926.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/244/FIGURE-171169.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/243/FIGURE-174007.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/231/FIGURE-152018.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/204/FIGURE-119561.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/244/FIGURE-177576.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/244/FIGURE-180343.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/251/FIGURE-182741.jpg</t>
   </si>
   <si>
     <t>https://img.amiami.com/images/product/main/242/FIGURE-171858.jpg</t>
@@ -148,7 +658,25 @@
     <t>https://img.amiami.com/images/product/main/252/FIGURE-185231.jpg</t>
   </si>
   <si>
-    <t>https://img.amiami.com/images/product/main/252/FIGURE-185101.jpg</t>
+    <t>https://img.amiami.com/images/product/main/252/FIGURE-187543.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/252/FIGURE-184860.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/253/FIGURE-191901.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/243/FIGURE-173862.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/252/FIGURE-186836.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/251/FIGURE-184035.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/162/FIGURE-019476.jpg</t>
   </si>
   <si>
     <t>https://img.amiami.com/images/product/main/252/FIGURE-185454.jpg</t>
@@ -160,25 +688,166 @@
     <t>https://img.amiami.com/images/product/main/253/FIGURE-189605.jpg</t>
   </si>
   <si>
-    <t>https://img.amiami.com/images/product/main/252/FIGURE-185281.jpg</t>
+    <t>https://img.amiami.com/images/product/main/233/FIGURE-159024.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/214/FIGURE-133587.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/193/FIGURE-049232.jpg</t>
   </si>
   <si>
     <t>https://img.amiami.com/images/product/main/251/FIGURE-181818.jpg</t>
   </si>
   <si>
+    <t>6,750 JPY</t>
+  </si>
+  <si>
+    <t>8,980 JPY</t>
+  </si>
+  <si>
     <t>11,000 JPY</t>
   </si>
   <si>
-    <t>6,776 JPY</t>
+    <t>13,050 JPY</t>
+  </si>
+  <si>
+    <t>3,650 JPY</t>
+  </si>
+  <si>
+    <t>19,250 JPY</t>
+  </si>
+  <si>
+    <t>17,440 JPY</t>
+  </si>
+  <si>
+    <t>10,780 JPY</t>
+  </si>
+  <si>
+    <t>15,580 JPY</t>
+  </si>
+  <si>
+    <t>12,580 JPY</t>
+  </si>
+  <si>
+    <t>16,980 JPY</t>
+  </si>
+  <si>
+    <t>11,880 JPY</t>
+  </si>
+  <si>
+    <t>15,840 JPY</t>
+  </si>
+  <si>
+    <t>9,410 JPY</t>
+  </si>
+  <si>
+    <t>17,550 JPY</t>
+  </si>
+  <si>
+    <t>15,980 JPY</t>
+  </si>
+  <si>
+    <t>15,015 JPY</t>
+  </si>
+  <si>
+    <t>14,380 JPY</t>
+  </si>
+  <si>
+    <t>14,500 JPY</t>
+  </si>
+  <si>
+    <t>17,980 JPY</t>
+  </si>
+  <si>
+    <t>13,480 JPY</t>
+  </si>
+  <si>
+    <t>23,830 JPY</t>
+  </si>
+  <si>
+    <t>15,240 JPY</t>
+  </si>
+  <si>
+    <t>29,260 JPY</t>
+  </si>
+  <si>
+    <t>32,340 JPY</t>
+  </si>
+  <si>
+    <t>25,564 JPY</t>
+  </si>
+  <si>
+    <t>12,320 JPY</t>
+  </si>
+  <si>
+    <t>15,420 JPY</t>
+  </si>
+  <si>
+    <t>17,180 JPY</t>
   </si>
   <si>
     <t>22,935 JPY</t>
   </si>
   <si>
+    <t>22,275 JPY</t>
+  </si>
+  <si>
+    <t>6,280 JPY</t>
+  </si>
+  <si>
+    <t>29,980 JPY</t>
+  </si>
+  <si>
+    <t>23,380 JPY</t>
+  </si>
+  <si>
+    <t>32,780 JPY</t>
+  </si>
+  <si>
+    <t>19,980 JPY</t>
+  </si>
+  <si>
+    <t>35,112 JPY</t>
+  </si>
+  <si>
+    <t>20,160 JPY</t>
+  </si>
+  <si>
+    <t>17,600 JPY</t>
+  </si>
+  <si>
+    <t>22,000 JPY</t>
+  </si>
+  <si>
+    <t>25,307 JPY</t>
+  </si>
+  <si>
+    <t>18,480 JPY</t>
+  </si>
+  <si>
+    <t>21,580 JPY</t>
+  </si>
+  <si>
+    <t>19,780 JPY</t>
+  </si>
+  <si>
+    <t>22,480 JPY</t>
+  </si>
+  <si>
+    <t>14,480 JPY</t>
+  </si>
+  <si>
     <t>16,830 JPY</t>
   </si>
   <si>
-    <t>27,520 JPY</t>
+    <t>30,780 JPY</t>
+  </si>
+  <si>
+    <t>28,500 JPY</t>
+  </si>
+  <si>
+    <t>22,470 JPY</t>
   </si>
   <si>
     <t>29,520 JPY</t>
@@ -187,7 +856,16 @@
     <t>21,420 JPY</t>
   </si>
   <si>
-    <t>28,980 JPY</t>
+    <t>26,730 JPY</t>
+  </si>
+  <si>
+    <t>18,810 JPY</t>
+  </si>
+  <si>
+    <t>19,740 JPY</t>
+  </si>
+  <si>
+    <t>12,480 JPY</t>
   </si>
   <si>
     <t>23,820 JPY</t>
@@ -196,25 +874,133 @@
     <t>21,660 JPY</t>
   </si>
   <si>
-    <t>18,810 JPY</t>
-  </si>
-  <si>
-    <t>25,720 JPY</t>
+    <t>15,280 JPY</t>
+  </si>
+  <si>
+    <t>22,940 JPY</t>
+  </si>
+  <si>
+    <t>19,350 JPY</t>
+  </si>
+  <si>
+    <t>32,080 JPY</t>
   </si>
   <si>
     <t>22,630 JPY</t>
   </si>
   <si>
+    <t>17,380 JPY</t>
+  </si>
+  <si>
+    <t>22,880 JPY</t>
+  </si>
+  <si>
     <t>23,650 JPY</t>
   </si>
   <si>
-    <t>9,680 JPY</t>
+    <t>27,280 JPY</t>
+  </si>
+  <si>
+    <t>7,480 JPY</t>
+  </si>
+  <si>
+    <t>38,500 JPY</t>
+  </si>
+  <si>
+    <t>34,100 JPY</t>
+  </si>
+  <si>
+    <t>19,900 JPY</t>
+  </si>
+  <si>
+    <t>19,800 JPY</t>
+  </si>
+  <si>
+    <t>28,380 JPY</t>
+  </si>
+  <si>
+    <t>26,400 JPY</t>
+  </si>
+  <si>
+    <t>15,180 JPY</t>
+  </si>
+  <si>
+    <t>27,900 JPY</t>
+  </si>
+  <si>
+    <t>25,300 JPY</t>
+  </si>
+  <si>
+    <t>23,100 JPY</t>
+  </si>
+  <si>
+    <t>26,800 JPY</t>
+  </si>
+  <si>
+    <t>34,800 JPY</t>
+  </si>
+  <si>
+    <t>21,780 JPY</t>
+  </si>
+  <si>
+    <t>41,800 JPY</t>
+  </si>
+  <si>
+    <t>46,200 JPY</t>
+  </si>
+  <si>
+    <t>36,520 JPY</t>
   </si>
   <si>
     <t>30,580 JPY</t>
   </si>
   <si>
-    <t>19,800 JPY</t>
+    <t>29,700 JPY</t>
+  </si>
+  <si>
+    <t>8,360 JPY</t>
+  </si>
+  <si>
+    <t>39,600 JPY</t>
+  </si>
+  <si>
+    <t>30,800 JPY</t>
+  </si>
+  <si>
+    <t>42,460 JPY</t>
+  </si>
+  <si>
+    <t>25,200 JPY</t>
+  </si>
+  <si>
+    <t>43,890 JPY</t>
+  </si>
+  <si>
+    <t>27,500 JPY</t>
+  </si>
+  <si>
+    <t>31,634 JPY</t>
+  </si>
+  <si>
+    <t>29,150 JPY</t>
+  </si>
+  <si>
+    <t>24,200 JPY</t>
+  </si>
+  <si>
+    <t>27,000 JPY</t>
+  </si>
+  <si>
+    <t>17,050 JPY</t>
+  </si>
+  <si>
+    <t>36,080 JPY</t>
+  </si>
+  <si>
+    <t>31,680 JPY</t>
+  </si>
+  <si>
+    <t>24,970 JPY</t>
   </si>
   <si>
     <t>32,800 JPY</t>
@@ -223,37 +1009,169 @@
     <t>23,800 JPY</t>
   </si>
   <si>
+    <t>18,700 JPY</t>
+  </si>
+  <si>
+    <t>20,900 JPY</t>
+  </si>
+  <si>
+    <t>21,230 JPY</t>
+  </si>
+  <si>
+    <t>13,200 JPY</t>
+  </si>
+  <si>
     <t>25,080 JPY</t>
   </si>
   <si>
     <t>22,800 JPY</t>
   </si>
   <si>
-    <t>26,800 JPY</t>
-  </si>
-  <si>
-    <t>23,100 JPY</t>
+    <t>15,800 JPY</t>
+  </si>
+  <si>
+    <t>13,915 JPY</t>
+  </si>
+  <si>
+    <t>61.16%</t>
+  </si>
+  <si>
+    <t>60.75%</t>
   </si>
   <si>
     <t>53.49%</t>
   </si>
   <si>
+    <t>52.16%</t>
+  </si>
+  <si>
+    <t>51.2%</t>
+  </si>
+  <si>
+    <t>50.0%</t>
+  </si>
+  <si>
+    <t>48.86%</t>
+  </si>
+  <si>
+    <t>45.83%</t>
+  </si>
+  <si>
+    <t>45.56%</t>
+  </si>
+  <si>
+    <t>42.89%</t>
+  </si>
+  <si>
+    <t>42.82%</t>
+  </si>
+  <si>
+    <t>40.17%</t>
+  </si>
+  <si>
+    <t>40.0%</t>
+  </si>
+  <si>
+    <t>38.01%</t>
+  </si>
+  <si>
+    <t>37.1%</t>
+  </si>
+  <si>
+    <t>36.84%</t>
+  </si>
+  <si>
+    <t>35.0%</t>
+  </si>
+  <si>
+    <t>34.64%</t>
+  </si>
+  <si>
+    <t>34.09%</t>
+  </si>
+  <si>
+    <t>32.91%</t>
+  </si>
+  <si>
+    <t>31.92%</t>
+  </si>
+  <si>
+    <t>31.52%</t>
+  </si>
+  <si>
+    <t>30.03%</t>
+  </si>
+  <si>
     <t>30.0%</t>
   </si>
   <si>
+    <t>29.2%</t>
+  </si>
+  <si>
+    <t>27.36%</t>
+  </si>
+  <si>
     <t>25.0%</t>
   </si>
   <si>
+    <t>24.88%</t>
+  </si>
+  <si>
+    <t>24.29%</t>
+  </si>
+  <si>
+    <t>24.09%</t>
+  </si>
+  <si>
+    <t>22.8%</t>
+  </si>
+  <si>
+    <t>20.71%</t>
+  </si>
+  <si>
+    <t>20.0%</t>
+  </si>
+  <si>
+    <t>19.79%</t>
+  </si>
+  <si>
+    <t>19.48%</t>
+  </si>
+  <si>
+    <t>18.27%</t>
+  </si>
+  <si>
+    <t>18.26%</t>
+  </si>
+  <si>
+    <t>16.74%</t>
+  </si>
+  <si>
+    <t>15.07%</t>
+  </si>
+  <si>
     <t>15.0%</t>
   </si>
   <si>
+    <t>14.69%</t>
+  </si>
+  <si>
+    <t>10.04%</t>
+  </si>
+  <si>
     <t>10.01%</t>
   </si>
   <si>
     <t>10.0%</t>
   </si>
   <si>
-    <t>5.23%</t>
+    <t>9.19%</t>
+  </si>
+  <si>
+    <t>7.02%</t>
+  </si>
+  <si>
+    <t>5.45%</t>
   </si>
   <si>
     <t>5.02%</t>
@@ -262,7 +1180,19 @@
     <t>5.0%</t>
   </si>
   <si>
-    <t>4.03%</t>
+    <t>3.29%</t>
+  </si>
+  <si>
+    <t>3.13%</t>
+  </si>
+  <si>
+    <t>3.0%</t>
+  </si>
+  <si>
+    <t>2.27%</t>
+  </si>
+  <si>
+    <t>2.2%</t>
   </si>
   <si>
     <t>2.03%</t>
@@ -639,12 +1569,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
     <col min="2" max="2" width="50.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="56.7109375" customWidth="1"/>
+    <col min="3" max="3" width="58.7109375" customWidth="1"/>
     <col min="4" max="4" width="66.7109375" customWidth="1"/>
     <col min="5" max="5" width="18.7109375" customWidth="1"/>
     <col min="6" max="6" width="16.7109375" customWidth="1"/>
@@ -679,22 +1609,22 @@
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>36</v>
+        <v>156</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>227</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>290</v>
       </c>
       <c r="G2" t="s">
-        <v>72</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -702,45 +1632,45 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>37</v>
+        <v>157</v>
       </c>
       <c r="E3" t="s">
-        <v>50</v>
+        <v>228</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>291</v>
       </c>
       <c r="G3" t="s">
-        <v>73</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>38</v>
+        <v>158</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>229</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>292</v>
       </c>
       <c r="G4" t="s">
-        <v>74</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -748,233 +1678,1636 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>39</v>
+        <v>159</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>230</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>293</v>
       </c>
       <c r="G5" t="s">
-        <v>75</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>40</v>
+        <v>160</v>
       </c>
       <c r="E6" t="s">
-        <v>53</v>
+        <v>231</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>294</v>
       </c>
       <c r="G6" t="s">
-        <v>76</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>41</v>
+        <v>161</v>
       </c>
       <c r="E7" t="s">
-        <v>54</v>
+        <v>232</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>295</v>
       </c>
       <c r="G7" t="s">
-        <v>77</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>42</v>
+        <v>162</v>
       </c>
       <c r="E8" t="s">
-        <v>55</v>
+        <v>233</v>
       </c>
       <c r="F8" t="s">
-        <v>67</v>
+        <v>296</v>
       </c>
       <c r="G8" t="s">
-        <v>77</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>43</v>
+        <v>163</v>
       </c>
       <c r="E9" t="s">
-        <v>56</v>
+        <v>234</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>297</v>
       </c>
       <c r="G9" t="s">
-        <v>78</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>31</v>
+        <v>90</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>44</v>
+        <v>164</v>
       </c>
       <c r="E10" t="s">
-        <v>57</v>
+        <v>234</v>
       </c>
       <c r="F10" t="s">
-        <v>68</v>
+        <v>298</v>
       </c>
       <c r="G10" t="s">
-        <v>79</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>45</v>
+        <v>165</v>
       </c>
       <c r="E11" t="s">
-        <v>58</v>
+        <v>235</v>
       </c>
       <c r="F11" t="s">
-        <v>69</v>
+        <v>293</v>
       </c>
       <c r="G11" t="s">
-        <v>80</v>
+        <v>347</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>46</v>
+        <v>166</v>
       </c>
       <c r="E12" t="s">
-        <v>59</v>
+        <v>236</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>266</v>
       </c>
       <c r="G12" t="s">
-        <v>80</v>
+        <v>348</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>47</v>
+        <v>167</v>
       </c>
       <c r="E13" t="s">
-        <v>60</v>
+        <v>237</v>
       </c>
       <c r="F13" t="s">
-        <v>70</v>
+        <v>299</v>
       </c>
       <c r="G13" t="s">
-        <v>81</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E14" t="s">
+        <v>238</v>
+      </c>
+      <c r="F14" t="s">
+        <v>298</v>
+      </c>
+      <c r="G14" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E15" t="s">
+        <v>239</v>
+      </c>
+      <c r="F15" t="s">
+        <v>300</v>
+      </c>
+      <c r="G15" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E16" t="s">
+        <v>240</v>
+      </c>
+      <c r="F16" t="s">
+        <v>301</v>
+      </c>
+      <c r="G16" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E17" t="s">
+        <v>241</v>
+      </c>
+      <c r="F17" t="s">
+        <v>302</v>
+      </c>
+      <c r="G17" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="B18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E18" t="s">
+        <v>242</v>
+      </c>
+      <c r="F18" t="s">
+        <v>303</v>
+      </c>
+      <c r="G18" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E19" t="s">
+        <v>243</v>
+      </c>
+      <c r="F19" t="s">
+        <v>304</v>
+      </c>
+      <c r="G19" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E20" t="s">
+        <v>244</v>
+      </c>
+      <c r="F20" t="s">
+        <v>266</v>
+      </c>
+      <c r="G20" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E21" t="s">
+        <v>245</v>
+      </c>
+      <c r="F21" t="s">
+        <v>266</v>
+      </c>
+      <c r="G21" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E22" t="s">
+        <v>246</v>
+      </c>
+      <c r="F22" t="s">
+        <v>305</v>
+      </c>
+      <c r="G22" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E23" t="s">
+        <v>247</v>
+      </c>
+      <c r="F23" t="s">
+        <v>298</v>
+      </c>
+      <c r="G23" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E24" t="s">
+        <v>248</v>
+      </c>
+      <c r="F24" t="s">
+        <v>306</v>
+      </c>
+      <c r="G24" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E25" t="s">
+        <v>249</v>
+      </c>
+      <c r="F25" t="s">
+        <v>307</v>
+      </c>
+      <c r="G25" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="C26" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E26" t="s">
+        <v>250</v>
+      </c>
+      <c r="F26" t="s">
+        <v>308</v>
+      </c>
+      <c r="G26" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E27" t="s">
+        <v>251</v>
+      </c>
+      <c r="F27" t="s">
+        <v>309</v>
+      </c>
+      <c r="G27" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E28" t="s">
+        <v>252</v>
+      </c>
+      <c r="F28" t="s">
+        <v>310</v>
+      </c>
+      <c r="G28" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E29" t="s">
+        <v>253</v>
+      </c>
+      <c r="F29" t="s">
+        <v>265</v>
+      </c>
+      <c r="G29" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E30" t="s">
+        <v>254</v>
+      </c>
+      <c r="F30" t="s">
+        <v>307</v>
+      </c>
+      <c r="G30" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E31" t="s">
+        <v>242</v>
+      </c>
+      <c r="F31" t="s">
+        <v>266</v>
+      </c>
+      <c r="G31" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E32" t="s">
+        <v>242</v>
+      </c>
+      <c r="F32" t="s">
+        <v>266</v>
+      </c>
+      <c r="G32" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E33" t="s">
+        <v>255</v>
+      </c>
+      <c r="F33" t="s">
+        <v>292</v>
+      </c>
+      <c r="G33" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E34" t="s">
+        <v>256</v>
+      </c>
+      <c r="F34" t="s">
+        <v>311</v>
+      </c>
+      <c r="G34" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E35" t="s">
+        <v>257</v>
+      </c>
+      <c r="F35" t="s">
+        <v>312</v>
+      </c>
+      <c r="G35" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E36" t="s">
+        <v>258</v>
+      </c>
+      <c r="F36" t="s">
+        <v>313</v>
+      </c>
+      <c r="G36" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E37" t="s">
+        <v>259</v>
+      </c>
+      <c r="F37" t="s">
+        <v>314</v>
+      </c>
+      <c r="G37" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E38" t="s">
+        <v>260</v>
+      </c>
+      <c r="F38" t="s">
+        <v>315</v>
+      </c>
+      <c r="G38" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E14" t="s">
+      <c r="C39" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E39" t="s">
+        <v>261</v>
+      </c>
+      <c r="F39" t="s">
+        <v>316</v>
+      </c>
+      <c r="G39" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>10</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E40" t="s">
+        <v>262</v>
+      </c>
+      <c r="F40" t="s">
+        <v>317</v>
+      </c>
+      <c r="G40" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" t="s">
+        <v>10</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E41" t="s">
+        <v>263</v>
+      </c>
+      <c r="F41" t="s">
+        <v>318</v>
+      </c>
+      <c r="G41" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E42" t="s">
+        <v>264</v>
+      </c>
+      <c r="F42" t="s">
+        <v>317</v>
+      </c>
+      <c r="G42" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E43" t="s">
+        <v>265</v>
+      </c>
+      <c r="F43" t="s">
+        <v>266</v>
+      </c>
+      <c r="G43" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E44" t="s">
+        <v>266</v>
+      </c>
+      <c r="F44" t="s">
+        <v>319</v>
+      </c>
+      <c r="G44" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" t="s">
+        <v>10</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E45" t="s">
+        <v>267</v>
+      </c>
+      <c r="F45" t="s">
+        <v>320</v>
+      </c>
+      <c r="G45" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" t="s">
+        <v>10</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E46" t="s">
+        <v>265</v>
+      </c>
+      <c r="F46" t="s">
+        <v>266</v>
+      </c>
+      <c r="G46" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" t="s">
+        <v>10</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E47" t="s">
+        <v>268</v>
+      </c>
+      <c r="F47" t="s">
+        <v>304</v>
+      </c>
+      <c r="G47" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E48" t="s">
+        <v>260</v>
+      </c>
+      <c r="F48" t="s">
+        <v>321</v>
+      </c>
+      <c r="G48" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E49" t="s">
+        <v>269</v>
+      </c>
+      <c r="F49" t="s">
+        <v>305</v>
+      </c>
+      <c r="G49" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E50" t="s">
+        <v>246</v>
+      </c>
+      <c r="F50" t="s">
+        <v>266</v>
+      </c>
+      <c r="G50" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E51" t="s">
+        <v>270</v>
+      </c>
+      <c r="F51" t="s">
+        <v>322</v>
+      </c>
+      <c r="G51" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F14" t="s">
+      <c r="C52" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E52" t="s">
+        <v>271</v>
+      </c>
+      <c r="F52" t="s">
+        <v>323</v>
+      </c>
+      <c r="G52" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E53" t="s">
+        <v>272</v>
+      </c>
+      <c r="F53" t="s">
+        <v>324</v>
+      </c>
+      <c r="G53" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
+        <v>8</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E54" t="s">
+        <v>273</v>
+      </c>
+      <c r="F54" t="s">
+        <v>298</v>
+      </c>
+      <c r="G54" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>9</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E55" t="s">
+        <v>274</v>
+      </c>
+      <c r="F55" t="s">
+        <v>325</v>
+      </c>
+      <c r="G55" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>10</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E56" t="s">
+        <v>275</v>
+      </c>
+      <c r="F56" t="s">
+        <v>326</v>
+      </c>
+      <c r="G56" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" t="s">
+        <v>10</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E57" t="s">
+        <v>276</v>
+      </c>
+      <c r="F57" t="s">
+        <v>327</v>
+      </c>
+      <c r="G57" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" t="s">
+        <v>8</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E58" t="s">
+        <v>277</v>
+      </c>
+      <c r="F58" t="s">
+        <v>328</v>
+      </c>
+      <c r="G58" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" t="s">
+        <v>10</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E59" t="s">
+        <v>278</v>
+      </c>
+      <c r="F59" t="s">
+        <v>329</v>
+      </c>
+      <c r="G59" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
+        <v>10</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E60" t="s">
+        <v>279</v>
+      </c>
+      <c r="F60" t="s">
+        <v>312</v>
+      </c>
+      <c r="G60" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" t="s">
+        <v>10</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E61" t="s">
+        <v>273</v>
+      </c>
+      <c r="F61" t="s">
+        <v>330</v>
+      </c>
+      <c r="G61" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
+        <v>10</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E62" t="s">
+        <v>280</v>
+      </c>
+      <c r="F62" t="s">
+        <v>331</v>
+      </c>
+      <c r="G62" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>10</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G14" t="s">
-        <v>82</v>
+      <c r="C63" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E63" t="s">
+        <v>273</v>
+      </c>
+      <c r="F63" t="s">
+        <v>330</v>
+      </c>
+      <c r="G63" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>7</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E64" t="s">
+        <v>246</v>
+      </c>
+      <c r="F64" t="s">
+        <v>298</v>
+      </c>
+      <c r="G64" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
+        <v>10</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E65" t="s">
+        <v>281</v>
+      </c>
+      <c r="F65" t="s">
+        <v>332</v>
+      </c>
+      <c r="G65" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" t="s">
+        <v>7</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E66" t="s">
+        <v>282</v>
+      </c>
+      <c r="F66" t="s">
+        <v>333</v>
+      </c>
+      <c r="G66" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" t="s">
+        <v>10</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E67" t="s">
+        <v>283</v>
+      </c>
+      <c r="F67" t="s">
+        <v>334</v>
+      </c>
+      <c r="G67" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" t="s">
+        <v>10</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E68" t="s">
+        <v>284</v>
+      </c>
+      <c r="F68" t="s">
+        <v>335</v>
+      </c>
+      <c r="G68" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" t="s">
+        <v>10</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E69" t="s">
+        <v>280</v>
+      </c>
+      <c r="F69" t="s">
+        <v>298</v>
+      </c>
+      <c r="G69" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" t="s">
+        <v>7</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E70" t="s">
+        <v>285</v>
+      </c>
+      <c r="F70" t="s">
+        <v>336</v>
+      </c>
+      <c r="G70" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" t="s">
+        <v>7</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E71" t="s">
+        <v>247</v>
+      </c>
+      <c r="F71" t="s">
+        <v>337</v>
+      </c>
+      <c r="G71" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" t="s">
+        <v>10</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E72" t="s">
+        <v>286</v>
+      </c>
+      <c r="F72" t="s">
+        <v>292</v>
+      </c>
+      <c r="G72" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" t="s">
+        <v>7</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E73" t="s">
+        <v>287</v>
+      </c>
+      <c r="F73" t="s">
+        <v>298</v>
+      </c>
+      <c r="G73" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" t="s">
+        <v>7</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E74" t="s">
+        <v>288</v>
+      </c>
+      <c r="F74" t="s">
+        <v>328</v>
+      </c>
+      <c r="G74" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" t="s">
+        <v>10</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E75" t="s">
+        <v>289</v>
+      </c>
+      <c r="F75" t="s">
+        <v>304</v>
+      </c>
+      <c r="G75" t="s">
+        <v>392</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G14"/>
+  <autoFilter ref="A1:G75"/>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1"/>
     <hyperlink ref="D2" r:id="rId2"/>
@@ -1002,6 +3335,128 @@
     <hyperlink ref="D13" r:id="rId24"/>
     <hyperlink ref="C14" r:id="rId25"/>
     <hyperlink ref="D14" r:id="rId26"/>
+    <hyperlink ref="C15" r:id="rId27"/>
+    <hyperlink ref="D15" r:id="rId28"/>
+    <hyperlink ref="C16" r:id="rId29"/>
+    <hyperlink ref="D16" r:id="rId30"/>
+    <hyperlink ref="C17" r:id="rId31"/>
+    <hyperlink ref="D17" r:id="rId32"/>
+    <hyperlink ref="C18" r:id="rId33"/>
+    <hyperlink ref="D18" r:id="rId34"/>
+    <hyperlink ref="C19" r:id="rId35"/>
+    <hyperlink ref="D19" r:id="rId36"/>
+    <hyperlink ref="C20" r:id="rId37"/>
+    <hyperlink ref="D20" r:id="rId38"/>
+    <hyperlink ref="C21" r:id="rId39"/>
+    <hyperlink ref="D21" r:id="rId40"/>
+    <hyperlink ref="C22" r:id="rId41"/>
+    <hyperlink ref="D22" r:id="rId42"/>
+    <hyperlink ref="C23" r:id="rId43"/>
+    <hyperlink ref="D23" r:id="rId44"/>
+    <hyperlink ref="C24" r:id="rId45"/>
+    <hyperlink ref="D24" r:id="rId46"/>
+    <hyperlink ref="C25" r:id="rId47"/>
+    <hyperlink ref="D25" r:id="rId48"/>
+    <hyperlink ref="C26" r:id="rId49"/>
+    <hyperlink ref="D26" r:id="rId50"/>
+    <hyperlink ref="C27" r:id="rId51"/>
+    <hyperlink ref="D27" r:id="rId52"/>
+    <hyperlink ref="C28" r:id="rId53"/>
+    <hyperlink ref="D28" r:id="rId54"/>
+    <hyperlink ref="C29" r:id="rId55"/>
+    <hyperlink ref="D29" r:id="rId56"/>
+    <hyperlink ref="C30" r:id="rId57"/>
+    <hyperlink ref="D30" r:id="rId58"/>
+    <hyperlink ref="C31" r:id="rId59"/>
+    <hyperlink ref="D31" r:id="rId60"/>
+    <hyperlink ref="C32" r:id="rId61"/>
+    <hyperlink ref="D32" r:id="rId62"/>
+    <hyperlink ref="C33" r:id="rId63"/>
+    <hyperlink ref="D33" r:id="rId64"/>
+    <hyperlink ref="C34" r:id="rId65"/>
+    <hyperlink ref="D34" r:id="rId66"/>
+    <hyperlink ref="C35" r:id="rId67"/>
+    <hyperlink ref="D35" r:id="rId68"/>
+    <hyperlink ref="C36" r:id="rId69"/>
+    <hyperlink ref="D36" r:id="rId70"/>
+    <hyperlink ref="C37" r:id="rId71"/>
+    <hyperlink ref="D37" r:id="rId72"/>
+    <hyperlink ref="C38" r:id="rId73"/>
+    <hyperlink ref="D38" r:id="rId74"/>
+    <hyperlink ref="C39" r:id="rId75"/>
+    <hyperlink ref="D39" r:id="rId76"/>
+    <hyperlink ref="C40" r:id="rId77"/>
+    <hyperlink ref="D40" r:id="rId78"/>
+    <hyperlink ref="C41" r:id="rId79"/>
+    <hyperlink ref="D41" r:id="rId80"/>
+    <hyperlink ref="C42" r:id="rId81"/>
+    <hyperlink ref="D42" r:id="rId82"/>
+    <hyperlink ref="C43" r:id="rId83"/>
+    <hyperlink ref="D43" r:id="rId84"/>
+    <hyperlink ref="C44" r:id="rId85"/>
+    <hyperlink ref="D44" r:id="rId86"/>
+    <hyperlink ref="C45" r:id="rId87"/>
+    <hyperlink ref="D45" r:id="rId88"/>
+    <hyperlink ref="C46" r:id="rId89"/>
+    <hyperlink ref="D46" r:id="rId90"/>
+    <hyperlink ref="C47" r:id="rId91"/>
+    <hyperlink ref="D47" r:id="rId92"/>
+    <hyperlink ref="C48" r:id="rId93"/>
+    <hyperlink ref="D48" r:id="rId94"/>
+    <hyperlink ref="C49" r:id="rId95"/>
+    <hyperlink ref="D49" r:id="rId96"/>
+    <hyperlink ref="C50" r:id="rId97"/>
+    <hyperlink ref="D50" r:id="rId98"/>
+    <hyperlink ref="C51" r:id="rId99"/>
+    <hyperlink ref="D51" r:id="rId100"/>
+    <hyperlink ref="C52" r:id="rId101"/>
+    <hyperlink ref="D52" r:id="rId102"/>
+    <hyperlink ref="C53" r:id="rId103"/>
+    <hyperlink ref="D53" r:id="rId104"/>
+    <hyperlink ref="C54" r:id="rId105"/>
+    <hyperlink ref="D54" r:id="rId106"/>
+    <hyperlink ref="C55" r:id="rId107"/>
+    <hyperlink ref="D55" r:id="rId108"/>
+    <hyperlink ref="C56" r:id="rId109"/>
+    <hyperlink ref="D56" r:id="rId110"/>
+    <hyperlink ref="C57" r:id="rId111"/>
+    <hyperlink ref="D57" r:id="rId112"/>
+    <hyperlink ref="C58" r:id="rId113"/>
+    <hyperlink ref="D58" r:id="rId114"/>
+    <hyperlink ref="C59" r:id="rId115"/>
+    <hyperlink ref="D59" r:id="rId116"/>
+    <hyperlink ref="C60" r:id="rId117"/>
+    <hyperlink ref="D60" r:id="rId118"/>
+    <hyperlink ref="C61" r:id="rId119"/>
+    <hyperlink ref="D61" r:id="rId120"/>
+    <hyperlink ref="C62" r:id="rId121"/>
+    <hyperlink ref="D62" r:id="rId122"/>
+    <hyperlink ref="C63" r:id="rId123"/>
+    <hyperlink ref="D63" r:id="rId124"/>
+    <hyperlink ref="C64" r:id="rId125"/>
+    <hyperlink ref="D64" r:id="rId126"/>
+    <hyperlink ref="C65" r:id="rId127"/>
+    <hyperlink ref="D65" r:id="rId128"/>
+    <hyperlink ref="C66" r:id="rId129"/>
+    <hyperlink ref="D66" r:id="rId130"/>
+    <hyperlink ref="C67" r:id="rId131"/>
+    <hyperlink ref="D67" r:id="rId132"/>
+    <hyperlink ref="C68" r:id="rId133"/>
+    <hyperlink ref="D68" r:id="rId134"/>
+    <hyperlink ref="C69" r:id="rId135"/>
+    <hyperlink ref="D69" r:id="rId136"/>
+    <hyperlink ref="C70" r:id="rId137"/>
+    <hyperlink ref="D70" r:id="rId138"/>
+    <hyperlink ref="C71" r:id="rId139"/>
+    <hyperlink ref="D71" r:id="rId140"/>
+    <hyperlink ref="C72" r:id="rId141"/>
+    <hyperlink ref="D72" r:id="rId142"/>
+    <hyperlink ref="C73" r:id="rId143"/>
+    <hyperlink ref="D73" r:id="rId144"/>
+    <hyperlink ref="C74" r:id="rId145"/>
+    <hyperlink ref="D74" r:id="rId146"/>
+    <hyperlink ref="C75" r:id="rId147"/>
+    <hyperlink ref="D75" r:id="rId148"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
